--- a/data/traffic_data.xlsx
+++ b/data/traffic_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/3.PC/Math_Concepts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A8D9242E-D69F-4441-B76E-1540F90406A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDD86D6E-78D4-43F4-8C19-DA9200533D15}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{A8D9242E-D69F-4441-B76E-1540F90406A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3B28AA1-08DA-4490-AE24-911F1B7F5D63}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
   </bookViews>
@@ -90,13 +90,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -107,7 +114,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -130,51 +137,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,110 +490,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F90EE7-EDBE-4B86-BDAE-F71BA6F047B2}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.875" customWidth="1"/>
-    <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A1:A2"/>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/traffic_data.xlsx
+++ b/data/traffic_data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/3.PC/Math_Concepts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boris\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{A8D9242E-D69F-4441-B76E-1540F90406A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3B28AA1-08DA-4490-AE24-911F1B7F5D63}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="load_equivalency_factor_BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -150,15 +150,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Нормален" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -491,22 +491,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F90EE7-EDBE-4B86-BDAE-F71BA6F047B2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -516,7 +516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -527,7 +527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -538,7 +538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -560,7 +560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>

--- a/data/traffic_data.xlsx
+++ b/data/traffic_data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boris\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/1.Finansova gramotnsot/Личен_финансов_план/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDA6B60E-0EBB-42AA-A594-84E69DBEED86}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
   </bookViews>
   <sheets>
     <sheet name="load_equivalency_factor_BG" sheetId="1" r:id="rId1"/>
+    <sheet name="total_weight" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,14 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>100 kN/axle</t>
   </si>
   <si>
-    <t>11,5 kN/axle</t>
-  </si>
-  <si>
     <t>0.03</t>
   </si>
   <si>
@@ -84,6 +82,216 @@
   </si>
   <si>
     <t>Buses</t>
+  </si>
+  <si>
+    <t>FK4-2</t>
+  </si>
+  <si>
+    <t>FK4-3</t>
+  </si>
+  <si>
+    <t>FK4-4</t>
+  </si>
+  <si>
+    <t>FK4-5</t>
+  </si>
+  <si>
+    <t>FK4-6</t>
+  </si>
+  <si>
+    <t>FK4-7</t>
+  </si>
+  <si>
+    <t>g1</t>
+  </si>
+  <si>
+    <t>μ1</t>
+  </si>
+  <si>
+    <t>σ1</t>
+  </si>
+  <si>
+    <t>g2</t>
+  </si>
+  <si>
+    <t>μ2</t>
+  </si>
+  <si>
+    <t>σ2</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
+  <si>
+    <t>N2</t>
+  </si>
+  <si>
+    <t>Total weight [kN]</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>181.2</t>
+  </si>
+  <si>
+    <t>41.87</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>262.6</t>
+  </si>
+  <si>
+    <t>64.82</t>
+  </si>
+  <si>
+    <t>223.07</t>
+  </si>
+  <si>
+    <t>327.42</t>
+  </si>
+  <si>
+    <t>285.68</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>208.4</t>
+  </si>
+  <si>
+    <t>49.21</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>302.3</t>
+  </si>
+  <si>
+    <t>68.91</t>
+  </si>
+  <si>
+    <t>257.61</t>
+  </si>
+  <si>
+    <t>371.21</t>
+  </si>
+  <si>
+    <t>274.65</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>295.2</t>
+  </si>
+  <si>
+    <t>84.72</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>404.9</t>
+  </si>
+  <si>
+    <t>32.88</t>
+  </si>
+  <si>
+    <t>379.92</t>
+  </si>
+  <si>
+    <t>437.78</t>
+  </si>
+  <si>
+    <t>398.44</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>254.4</t>
+  </si>
+  <si>
+    <t>58.59</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>336.9</t>
+  </si>
+  <si>
+    <t>64.93</t>
+  </si>
+  <si>
+    <t>312.99</t>
+  </si>
+  <si>
+    <t>401.83</t>
+  </si>
+  <si>
+    <t>368.96</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>247.3</t>
+  </si>
+  <si>
+    <t>48.95</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>380.4</t>
+  </si>
+  <si>
+    <t>67.37</t>
+  </si>
+  <si>
+    <t>296.25</t>
+  </si>
+  <si>
+    <t>447.77</t>
+  </si>
+  <si>
+    <t>373.53</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>407.1</t>
+  </si>
+  <si>
+    <t>34.94</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>305.7</t>
+  </si>
+  <si>
+    <t>88.79</t>
+  </si>
+  <si>
+    <t>442.04</t>
+  </si>
+  <si>
+    <t>394.49</t>
+  </si>
+  <si>
+    <t>412.56</t>
+  </si>
+  <si>
+    <t>11.5 kN/axle</t>
   </si>
 </sst>
 </file>
@@ -141,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -156,9 +364,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Нормален" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -491,84 +702,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F90EE7-EDBE-4B86-BDAE-F71BA6F047B2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B4" s="2">
         <v>0.2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -577,4 +788,245 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B791DBC-82ED-4566-B870-C772ACEBF2F5}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/traffic_data.xlsx
+++ b/data/traffic_data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/1.Finansova gramotnsot/Личен_финансов_план/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDA6B60E-0EBB-42AA-A594-84E69DBEED86}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97625ECA-34F7-4A0A-977E-11C26E622795}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
   </bookViews>
   <sheets>
     <sheet name="load_equivalency_factor_BG" sheetId="1" r:id="rId1"/>
     <sheet name="total_weight" sheetId="2" r:id="rId2"/>
+    <sheet name="Axle_weights" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
   <si>
     <t>100 kN/axle</t>
   </si>
@@ -292,6 +293,105 @@
   </si>
   <si>
     <t>11.5 kN/axle</t>
+  </si>
+  <si>
+    <t>70.57</t>
+  </si>
+  <si>
+    <t>89.84</t>
+  </si>
+  <si>
+    <t>60.68</t>
+  </si>
+  <si>
+    <t>61.7</t>
+  </si>
+  <si>
+    <t>65.11</t>
+  </si>
+  <si>
+    <t>88.38</t>
+  </si>
+  <si>
+    <t>61.07</t>
+  </si>
+  <si>
+    <t>60.07</t>
+  </si>
+  <si>
+    <t>73.5</t>
+  </si>
+  <si>
+    <t>98.85</t>
+  </si>
+  <si>
+    <t>74.94</t>
+  </si>
+  <si>
+    <t>72.83</t>
+  </si>
+  <si>
+    <t>74.26</t>
+  </si>
+  <si>
+    <t>70.84</t>
+  </si>
+  <si>
+    <t>90.59</t>
+  </si>
+  <si>
+    <t>66.69</t>
+  </si>
+  <si>
+    <t>71.59</t>
+  </si>
+  <si>
+    <t>74.28</t>
+  </si>
+  <si>
+    <t>86.28</t>
+  </si>
+  <si>
+    <t>68.86</t>
+  </si>
+  <si>
+    <t>76.75</t>
+  </si>
+  <si>
+    <t>74.89</t>
+  </si>
+  <si>
+    <t>75.31</t>
+  </si>
+  <si>
+    <t>104.51</t>
+  </si>
+  <si>
+    <t>78.19</t>
+  </si>
+  <si>
+    <t>79.32</t>
+  </si>
+  <si>
+    <t>79.42</t>
+  </si>
+  <si>
+    <t>Axle Weights [kN]</t>
+  </si>
+  <si>
+    <t>Axle 1</t>
+  </si>
+  <si>
+    <t>Axle 2</t>
+  </si>
+  <si>
+    <t>Axle 3</t>
+  </si>
+  <si>
+    <t>Axle 4</t>
+  </si>
+  <si>
+    <t>Alxle 5</t>
   </si>
 </sst>
 </file>
@@ -349,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -366,6 +466,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,10 +814,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1029,4 +1132,162 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB72918-78EE-4914-970C-50F36FC31071}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="5">
+        <v>69</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/traffic_data.xlsx
+++ b/data/traffic_data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/1.Finansova gramotnsot/Личен_финансов_план/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97625ECA-34F7-4A0A-977E-11C26E622795}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B151D6C1-B7B7-4CC2-B0D0-5A68F6DACA8F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
   </bookViews>
   <sheets>
     <sheet name="load_equivalency_factor_BG" sheetId="1" r:id="rId1"/>
     <sheet name="total_weight" sheetId="2" r:id="rId2"/>
     <sheet name="Axle_weights" sheetId="3" r:id="rId3"/>
+    <sheet name="Calculated_lef" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="135">
   <si>
     <t>100 kN/axle</t>
   </si>
@@ -292,9 +293,6 @@
     <t>412.56</t>
   </si>
   <si>
-    <t>11.5 kN/axle</t>
-  </si>
-  <si>
     <t>70.57</t>
   </si>
   <si>
@@ -392,6 +390,60 @@
   </si>
   <si>
     <t>Alxle 5</t>
+  </si>
+  <si>
+    <t>1.699</t>
+  </si>
+  <si>
+    <t>1.765</t>
+  </si>
+  <si>
+    <t>1.726</t>
+  </si>
+  <si>
+    <t>1.825</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>0.979</t>
+  </si>
+  <si>
+    <t>1.007</t>
+  </si>
+  <si>
+    <t>0.985</t>
+  </si>
+  <si>
+    <t>1.041</t>
+  </si>
+  <si>
+    <t>load equivalency factor dimension vehicle 100kN/Axle</t>
+  </si>
+  <si>
+    <t>load equivalency factor dimension vehicle  115kN/Axle</t>
+  </si>
+  <si>
+    <t>115 kN/axle</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium </t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>Very Heavy</t>
+  </si>
+  <si>
+    <t>Motorway</t>
+  </si>
+  <si>
+    <t>Value in the norm in BG</t>
   </si>
 </sst>
 </file>
@@ -449,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -466,6 +518,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -814,10 +869,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="7"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -827,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1149,22 +1204,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1172,16 +1227,16 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
@@ -1192,16 +1247,16 @@
         <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -1212,19 +1267,19 @@
         <v>17</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1232,19 +1287,19 @@
         <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="E5" s="5">
         <v>69</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1252,19 +1307,19 @@
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1272,19 +1327,107 @@
         <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>111</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0702A-A9CD-41F3-908C-272D20C3C606}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/traffic_data.xlsx
+++ b/data/traffic_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/1.Finansova gramotnsot/Личен_финансов_план/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B151D6C1-B7B7-4CC2-B0D0-5A68F6DACA8F}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F889E7A-9F23-4A18-B86F-FCF96BD1E5FC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
   </bookViews>
@@ -1352,13 +1352,13 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.125" customWidth="1"/>
     <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">

--- a/data/traffic_data.xlsx
+++ b/data/traffic_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/1.Finansova gramotnsot/Личен_финансов_план/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bobo\My Documents\08_SofUni\MathsConcepts\Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{9120428B-883C-4227-BAED-B29F0F18D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F889E7A-9F23-4A18-B86F-FCF96BD1E5FC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A38FF4-7AD3-448D-BC34-AD0EC93A38FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{36488911-5709-4C28-988A-E38B961F8D71}"/>
   </bookViews>
   <sheets>
     <sheet name="load_equivalency_factor_BG" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -431,9 +429,6 @@
     <t>Light</t>
   </si>
   <si>
-    <t xml:space="preserve">Medium </t>
-  </si>
-  <si>
     <t>Heavy</t>
   </si>
   <si>
@@ -444,6 +439,9 @@
   </si>
   <si>
     <t>Value in the norm in BG</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
 </sst>
 </file>
@@ -501,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -514,20 +512,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Нормален" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -860,21 +852,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F90EE7-EDBE-4B86-BDAE-F71BA6F047B2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -885,7 +877,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,7 +888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -907,7 +899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -918,7 +910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -929,7 +921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -951,236 +943,236 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B791DBC-82ED-4566-B870-C772ACEBF2F5}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1192,153 +1184,153 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB72918-78EE-4914-970C-50F36FC31071}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="2">
         <v>69</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="2" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1350,83 +1342,83 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0702A-A9CD-41F3-908C-272D20C3C606}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.125" customWidth="1"/>
-    <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.09765625" customWidth="1"/>
+    <col min="2" max="2" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
